--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2543-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2543-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC9289B3-B806-4C66-B67D-1C3CD64B024D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{125D19AC-E84C-4396-9010-C8552F6BAD7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{C2E2743E-C3A1-4B7E-960A-9B4D13DABC6A}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{1F9F5CF2-9F1A-4236-89AE-B5D71EC1FB56}"/>
   </bookViews>
   <sheets>
     <sheet name="2543-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1487,28 +1487,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9524160-76A1-4988-B2E7-2AF5CC253FE2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{865A9A03-1730-4166-B620-B66C20205923}">
   <dimension ref="A1:X39"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.375" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1542,7 +1542,7 @@
       <c r="W1" s="29"/>
       <c r="X1" s="21"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1578,7 +1578,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1698,7 +1698,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2025</v>
       </c>
@@ -1770,7 +1770,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>2024</v>
       </c>
@@ -1916,7 +1916,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -1990,7 +1990,7 @@
         <v>3.44</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2064,7 +2064,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2023</v>
       </c>
@@ -2136,7 +2136,7 @@
         <v>7.36</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="38">
         <v>2022</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>3.38</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2021</v>
       </c>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="38">
         <v>2020</v>
       </c>
@@ -2352,7 +2352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>2019</v>
       </c>
@@ -2424,7 +2424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="38">
         <v>2018</v>
       </c>
@@ -2496,7 +2496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2017</v>
       </c>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="38">
         <v>2016</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>3.75</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>2015</v>
       </c>
@@ -2712,7 +2712,7 @@
         <v>4.08</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="38">
         <v>2014</v>
       </c>
@@ -2784,7 +2784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>2013</v>
       </c>
@@ -2856,7 +2856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="38">
         <v>2012</v>
       </c>
@@ -2928,7 +2928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>2011</v>
       </c>
@@ -3000,7 +3000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="38">
         <v>2010</v>
       </c>
@@ -3072,7 +3072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <v>2009</v>
       </c>
@@ -3144,7 +3144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="38">
         <v>2008</v>
       </c>
@@ -3216,7 +3216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>2007</v>
       </c>
@@ -3288,7 +3288,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="38">
         <v>2006</v>
       </c>
@@ -3360,7 +3360,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2005</v>
       </c>
@@ -3432,7 +3432,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="38">
         <v>2004</v>
       </c>
@@ -3504,7 +3504,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>2003</v>
       </c>
@@ -3576,7 +3576,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="38">
         <v>2002</v>
       </c>
@@ -3648,7 +3648,7 @@
         <v>4.1399999999999997</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="36">
         <v>2001</v>
       </c>
@@ -3720,7 +3720,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="38">
         <v>2000</v>
       </c>
@@ -3792,7 +3792,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="36">
         <v>1999</v>
       </c>
@@ -3864,7 +3864,7 @@
         <v>36.1</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="38">
         <v>1998</v>
       </c>
@@ -3936,7 +3936,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="36">
         <v>1997</v>
       </c>
@@ -4008,7 +4008,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="38">
         <v>1996</v>
       </c>
@@ -4080,7 +4080,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="36">
         <v>1995</v>
       </c>
@@ -4152,7 +4152,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="38" t="s">
         <v>49</v>
       </c>
